--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487919_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487919_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2001</v>
+        <v>7.7135</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5854</v>
+        <v>6.275</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6147</v>
+        <v>1.4385</v>
       </c>
       <c r="G2" t="n">
         <v>3.5779</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0646</v>
+        <v>0.4489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5004999999999999</v>
+        <v>0.1891</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4359</v>
+        <v>0.2597</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5191</v>
+        <v>3.96</v>
       </c>
       <c r="E3" t="n">
-        <v>6.245</v>
+        <v>6.3336</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7259</v>
+        <v>-2.3736</v>
       </c>
       <c r="G3" t="n">
         <v>3.5601</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0235</v>
+        <v>0.4643</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6178</v>
+        <v>0.7063</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.242</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5213</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.216</v>
+        <v>0.7886</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.8243</v>
+        <v>1.605</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0403</v>
+        <v>-0.8164</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6991</v>
+        <v>0.3478</v>
       </c>
       <c r="H4" t="n">
-        <v>2.322</v>
+        <v>0.8891</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6229</v>
+        <v>-0.5413</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6298</v>
+        <v>2.4952</v>
       </c>
       <c r="K4" t="n">
         <v>1.4731</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1568</v>
+        <v>1.0221</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0693</v>
+        <v>-2.1474</v>
       </c>
       <c r="N4" t="n">
-        <v>0.849</v>
+        <v>-0.5839</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-1.5634</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0887</v>
+        <v>-0.0481</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0215</v>
+        <v>0.3772</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1102</v>
+        <v>-0.4253</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3538</v>
+        <v>0.697</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3538</v>
+        <v>0.8137</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1223</v>
+        <v>-0.0477</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9387</v>
+        <v>-1.7357</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8164</v>
+        <v>1.688</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3478</v>
+        <v>1.6991</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8891</v>
+        <v>2.322</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5413</v>
+        <v>-0.6229</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4952</v>
+        <v>1.6298</v>
       </c>
       <c r="K5" t="n">
         <v>1.4731</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0221</v>
+        <v>0.1568</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1474</v>
+        <v>0.0693</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5839</v>
+        <v>0.849</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5634</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7144</v>
+        <v>-0.3524</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2891</v>
+        <v>0.11</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4253</v>
+        <v>-0.4625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.697</v>
+        <v>-0.3538</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8137</v>
+        <v>-0.3538</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3315</v>
+        <v>-0.5541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.838</v>
+        <v>0.498</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1695</v>
+        <v>-1.0521</v>
       </c>
       <c r="G6" t="n">
         <v>-1.408</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3607</v>
+        <v>0.1381</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7111</v>
+        <v>0.371</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3503</v>
+        <v>-0.2329</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1168</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6784</v>
+        <v>-0.8486</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9771</v>
+        <v>1.541</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6556</v>
+        <v>-2.3896</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1103</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4893</v>
+        <v>0.3192</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5905</v>
+        <v>-0.0266</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0798</v>
+        <v>0.3458</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5142</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7897</v>
+        <v>-1.1196</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7887</v>
+        <v>-1.2948</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001</v>
+        <v>0.1752</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3075</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4821</v>
+        <v>0.1879</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4567</v>
+        <v>0.0372</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0254</v>
+        <v>0.1507</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0834</v>
+        <v>-2.1211</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.8429</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3662</v>
+        <v>-1.2782</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4121</v>
@@ -1156,13 +1156,13 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.047</v>
+        <v>-0.0847</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4005</v>
+        <v>0.2748</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4475</v>
+        <v>-0.3595</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1701</v>
+        <v>-2.4915</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9616</v>
+        <v>-1.2831</v>
       </c>
       <c r="F10" t="n">
         <v>-1.2084</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8572</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.792</v>
+        <v>0.4705</v>
       </c>
       <c r="U10" t="n">
         <v>0.06519999999999999</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. VERGARA HARBOE</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7025</v>
+        <v>-4.8772</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5376</v>
+        <v>-1.431</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1649</v>
+        <v>-3.4462</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1968</v>
+        <v>-3.7657</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4649</v>
+        <v>-0.7784</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.7319</v>
+        <v>-2.9873</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0779</v>
+        <v>-2.5533</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1639</v>
+        <v>-1.2029</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2418</v>
+        <v>-1.3504</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1189</v>
+        <v>-1.2124</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6288</v>
+        <v>0.4245</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4901</v>
+        <v>-1.6369</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2968</v>
+        <v>-0.4008</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9316</v>
+        <v>-0.0452</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6348</v>
+        <v>-0.3555</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5944</v>
+        <v>-1.7513</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6899</v>
+        <v>1.1675</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2843</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>G. VERGARA HARBOE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2724</v>
+        <v>-5.0491</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.65</v>
+        <v>-1.9429</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6224</v>
+        <v>-3.1061</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7657</v>
+        <v>-4.1968</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7784</v>
+        <v>-0.4649</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9873</v>
+        <v>-3.7319</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5533</v>
+        <v>-1.0779</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2029</v>
+        <v>0.1639</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3504</v>
+        <v>-1.2418</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2124</v>
+        <v>-3.1189</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4245</v>
+        <v>-0.6288</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6369</v>
+        <v>-2.4901</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.796</v>
+        <v>-0.0498</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2643</v>
+        <v>0.5263</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5317</v>
+        <v>-0.576</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7513</v>
+        <v>-0.5944</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1675</v>
+        <v>0.6899</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9188</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1867</v>
+        <v>-5.9006</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5976</v>
+        <v>-3.6051</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5891</v>
+        <v>-2.2955</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7685</v>
@@ -1468,13 +1468,13 @@
         <v>1.2487</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.342</v>
+        <v>-0.056</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7086</v>
+        <v>0.2839</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6334</v>
+        <v>-0.3398</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2843</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.1572</v>
+        <v>-10.5474</v>
       </c>
       <c r="E14" t="n">
-        <v>1.507200000000001</v>
+        <v>4.117099999999999</v>
       </c>
       <c r="F14" t="n">
         <v>-14.6644</v>
@@ -1546,13 +1546,13 @@
         <v>14.5683</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5073</v>
+        <v>1.1024</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6648000000000002</v>
+        <v>3.2745</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.172</v>
+        <v>-2.1721</v>
       </c>
       <c r="V14" t="n">
         <v>-4.8116</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.161899999999999</v>
+        <v>9.034700000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>7.363</v>
+        <v>6.5058</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7988</v>
+        <v>2.5289</v>
       </c>
       <c r="G15" t="n">
         <v>7.5573</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3882</v>
+        <v>0.261</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2421</v>
+        <v>0.3849</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8539</v>
+        <v>-0.1239</v>
       </c>
       <c r="V15" t="n">
         <v>1.0083</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7406</v>
+        <v>4.7137</v>
       </c>
       <c r="E16" t="n">
-        <v>2.817</v>
+        <v>2.7099</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9236</v>
+        <v>2.0038</v>
       </c>
       <c r="G16" t="n">
         <v>2.2754</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9969</v>
+        <v>0.97</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7887</v>
+        <v>0.6815</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2082</v>
+        <v>0.2884</v>
       </c>
       <c r="V16" t="n">
         <v>1.4683</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0528</v>
+        <v>4.5631</v>
       </c>
       <c r="E17" t="n">
-        <v>6.3125</v>
+        <v>6.4196</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2597</v>
+        <v>-1.8565</v>
       </c>
       <c r="G17" t="n">
         <v>7.5213</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.428</v>
+        <v>0.0824</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1338</v>
+        <v>-0.0266</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2942</v>
+        <v>0.109</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5845</v>
+        <v>3.2716</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9129</v>
+        <v>1.295</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6717</v>
+        <v>1.9766</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7891</v>
+        <v>3.1728</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3539</v>
+        <v>2.1408</v>
       </c>
       <c r="I18" t="n">
-        <v>1.143</v>
+        <v>1.032</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2952</v>
+        <v>1.8869</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4885</v>
+        <v>1.5734</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.3135</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4938</v>
+        <v>1.2858</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1346</v>
+        <v>0.5674</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3592</v>
+        <v>0.7185</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6904</v>
+        <v>0.4963</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4907</v>
+        <v>0.4487</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1997</v>
+        <v>0.0477</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5213</v>
+        <v>-0.8137</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3538</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>A. MOODY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2144</v>
+        <v>2.9348</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9735</v>
+        <v>2.7878</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2408</v>
+        <v>0.1469</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1728</v>
+        <v>1.5112</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1408</v>
+        <v>-0.1877</v>
       </c>
       <c r="I19" t="n">
-        <v>1.032</v>
+        <v>1.699</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8869</v>
+        <v>2.8626</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5734</v>
+        <v>0.4901</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3135</v>
+        <v>2.3725</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2858</v>
+        <v>-1.3513</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5674</v>
+        <v>-0.6778</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7185</v>
+        <v>-0.6735</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4391</v>
+        <v>0.3122</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1272</v>
+        <v>-0.0747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3119</v>
+        <v>0.3869</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8137</v>
+        <v>0.0708</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8137</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5299</v>
+        <v>2.5154</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4812</v>
+        <v>0.7341</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0487</v>
+        <v>1.7813</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6594</v>
+        <v>0.7891</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0831</v>
+        <v>-0.3539</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4237</v>
+        <v>1.143</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.251</v>
+        <v>0.2952</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0258</v>
+        <v>-0.4885</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7748</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4083</v>
+        <v>0.4938</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0573</v>
+        <v>0.1346</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.351</v>
+        <v>0.3592</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2923</v>
+        <v>0.6213</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8539</v>
+        <v>0.312</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5617</v>
+        <v>0.3093</v>
       </c>
       <c r="V20" t="n">
-        <v>2.6889</v>
+        <v>1.5213</v>
       </c>
       <c r="W20" t="n">
-        <v>2.9188</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MOODY</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0648</v>
+        <v>2.4139</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1449</v>
+        <v>2.1597</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0801</v>
+        <v>0.2542</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5112</v>
+        <v>-0.6594</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1877</v>
+        <v>-1.0831</v>
       </c>
       <c r="I21" t="n">
-        <v>1.699</v>
+        <v>0.4237</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8626</v>
+        <v>-0.251</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4901</v>
+        <v>-1.0258</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3725</v>
+        <v>0.7748</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3513</v>
+        <v>-0.4083</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6778</v>
+        <v>-0.0573</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6735</v>
+        <v>-0.351</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5578</v>
+        <v>0.1763</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7177</v>
+        <v>0.5325</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1599</v>
+        <v>-0.3562</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0708</v>
+        <v>2.6889</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0708</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7736</v>
+        <v>0.4003</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2622</v>
+        <v>0.798</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0358</v>
+        <v>-0.3977</v>
       </c>
       <c r="G22" t="n">
         <v>0.2603</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3772</v>
+        <v>-0.2034</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7705</v>
+        <v>-0.2347</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6067</v>
+        <v>0.0314</v>
       </c>
       <c r="V22" t="n">
         <v>1.5921</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8061</v>
+        <v>-2.6632</v>
       </c>
       <c r="E23" t="n">
         <v>-1.52</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.286</v>
+        <v>-1.1432</v>
       </c>
       <c r="G23" t="n">
         <v>-2.949</v>
@@ -2248,13 +2248,13 @@
         <v>0.4162</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2734</v>
+        <v>-0.1305</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1429</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9139</v>
+        <v>-5.6401</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1492</v>
+        <v>-3.5778</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7648</v>
+        <v>-2.0623</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6814</v>
@@ -2326,13 +2326,13 @@
         <v>0.2081</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2566</v>
+        <v>0.5304</v>
       </c>
       <c r="T24" t="n">
-        <v>0.531</v>
+        <v>0.1024</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7255</v>
+        <v>0.428</v>
       </c>
       <c r="V24" t="n">
         <v>0.4246</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.6981</v>
+        <v>-6.2439</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9336</v>
+        <v>-3.6477</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7645</v>
+        <v>-2.5962</v>
       </c>
       <c r="G25" t="n">
         <v>-5.8376</v>
@@ -2404,13 +2404,13 @@
         <v>2.0812</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1091</v>
+        <v>0.1767</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1893</v>
+        <v>0.3576</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9813</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.1572</v>
+        <v>15.3003</v>
       </c>
       <c r="E26" t="n">
         <v>14.6644</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5073</v>
+        <v>0.6357999999999997</v>
       </c>
       <c r="G26" t="n">
         <v>9.959999999999999</v>
@@ -2482,13 +2482,13 @@
         <v>11.4465</v>
       </c>
       <c r="S26" t="n">
-        <v>1.5072</v>
+        <v>3.6503</v>
       </c>
       <c r="T26" t="n">
-        <v>2.172000000000001</v>
+        <v>2.1722</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6648999999999998</v>
+        <v>1.4782</v>
       </c>
       <c r="V26" t="n">
         <v>4.8118</v>
